--- a/Data/National Accounts/PSA-05EOS_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-05EOS_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891D0704-504B-46E3-92F9-AF1931F1A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C61F385-1273-45D5-8119-96CAA36C43A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EOS" sheetId="1" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -223,6 +220,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -664,7 +664,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -674,7 +674,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -874,10 +874,10 @@
         <v>240419.65902523042</v>
       </c>
       <c r="Z12" s="8">
-        <v>247324.09970968968</v>
+        <v>239925.097208758</v>
       </c>
       <c r="AA12" s="8">
-        <v>266060.77765002818</v>
+        <v>250007.76483680651</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -1026,10 +1026,10 @@
         <v>2814.1388854800189</v>
       </c>
       <c r="Z13" s="8">
-        <v>2866.7143596240471</v>
+        <v>2868.7219031401205</v>
       </c>
       <c r="AA13" s="8">
-        <v>3228.8197748633361</v>
+        <v>3340.8071075617299</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -1479,13 +1479,13 @@
         <v>410901.54506312823</v>
       </c>
       <c r="Y16" s="8">
-        <v>460095.71776875551</v>
+        <v>460095.71776875574</v>
       </c>
       <c r="Z16" s="8">
         <v>517031.94724435621</v>
       </c>
       <c r="AA16" s="8">
-        <v>565251.39502377831</v>
+        <v>564089.98355157557</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -1634,10 +1634,10 @@
         <v>1578363.7124905353</v>
       </c>
       <c r="Z17" s="8">
-        <v>1764805.7488743786</v>
+        <v>1764813.6283972142</v>
       </c>
       <c r="AA17" s="8">
-        <v>1838711.4210373638</v>
+        <v>1834114.1159981941</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -1786,10 +1786,10 @@
         <v>278143.36940471595</v>
       </c>
       <c r="Z18" s="8">
-        <v>293714.41199392331</v>
+        <v>293923.61777757533</v>
       </c>
       <c r="AA18" s="8">
-        <v>292996.10746069229</v>
+        <v>293630.97480473702</v>
       </c>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
@@ -1938,10 +1938,10 @@
         <v>42402.252148115083</v>
       </c>
       <c r="Z19" s="8">
-        <v>53954.788212298241</v>
+        <v>50675.721810733347</v>
       </c>
       <c r="AA19" s="8">
-        <v>63097.262865116136</v>
+        <v>56338.465278954391</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -2188,10 +2188,10 @@
         <v>3165207.24824388</v>
       </c>
       <c r="Z21" s="11">
-        <v>3475594.1701444439</v>
+        <v>3465135.194091951</v>
       </c>
       <c r="AA21" s="11">
-        <v>3585114.9755339255</v>
+        <v>3557291.3032999127</v>
       </c>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
@@ -2505,7 +2505,7 @@
     </row>
     <row r="28" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:96" x14ac:dyDescent="0.2">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="31" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:96" x14ac:dyDescent="0.2">
@@ -2715,10 +2715,10 @@
         <v>177016.70084181798</v>
       </c>
       <c r="Z37" s="8">
-        <v>181081.73306587862</v>
+        <v>175603.60680803534</v>
       </c>
       <c r="AA37" s="8">
-        <v>192331.07723903703</v>
+        <v>180707.75277183051</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -2867,10 +2867,10 @@
         <v>2363.1069559154143</v>
       </c>
       <c r="Z38" s="8">
-        <v>2349.5719499920451</v>
+        <v>2351.2286811367039</v>
       </c>
       <c r="AA38" s="8">
-        <v>2597.4035185494022</v>
+        <v>2688.2966595696589</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -3326,7 +3326,7 @@
         <v>498325.58526167629</v>
       </c>
       <c r="AA41" s="8">
-        <v>536940.41003908112</v>
+        <v>535833.24136394029</v>
       </c>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
@@ -3475,10 +3475,10 @@
         <v>1323212.7078256726</v>
       </c>
       <c r="Z42" s="8">
-        <v>1445891.5615377445</v>
+        <v>1445897.9461777182</v>
       </c>
       <c r="AA42" s="8">
-        <v>1478802.9735690069</v>
+        <v>1475126.6631907797</v>
       </c>
       <c r="AB42" s="9"/>
       <c r="AC42" s="9"/>
@@ -3627,10 +3627,10 @@
         <v>231428.95397107856</v>
       </c>
       <c r="Z43" s="8">
-        <v>238717.45349654174</v>
+        <v>238885.88834474268</v>
       </c>
       <c r="AA43" s="8">
-        <v>233742.95091655428</v>
+        <v>234242.22922068619</v>
       </c>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
@@ -3779,10 +3779,10 @@
         <v>35942.886978205832</v>
       </c>
       <c r="Z44" s="8">
-        <v>44687.254966403307</v>
+        <v>41980.171447566558</v>
       </c>
       <c r="AA44" s="8">
-        <v>51337.77118080591</v>
+        <v>45864.521406808519</v>
       </c>
       <c r="AB44" s="9"/>
       <c r="AC44" s="9"/>
@@ -4029,10 +4029,10 @@
         <v>2674018.5239629387</v>
       </c>
       <c r="Z46" s="11">
-        <v>2886177.2807118208</v>
+        <v>2878168.5471544606</v>
       </c>
       <c r="AA46" s="11">
-        <v>2931512.7230943614</v>
+        <v>2910222.8412449416</v>
       </c>
       <c r="AB46" s="9"/>
       <c r="AC46" s="9"/>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="53" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:96" x14ac:dyDescent="0.2">
@@ -4356,7 +4356,7 @@
     </row>
     <row r="56" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:96" x14ac:dyDescent="0.2">
@@ -4470,7 +4470,7 @@
         <v>51</v>
       </c>
       <c r="Z60" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA60" s="15"/>
     </row>
@@ -4551,10 +4551,10 @@
         <v>32.305474702129175</v>
       </c>
       <c r="Y62" s="16">
-        <v>2.8718286651154017</v>
+        <v>-0.20570772726223652</v>
       </c>
       <c r="Z62" s="16">
-        <v>7.5757590798194485</v>
+        <v>4.2024230667605593</v>
       </c>
       <c r="AA62" s="16"/>
       <c r="AB62" s="9"/>
@@ -4696,10 +4696,10 @@
         <v>-3.181097532738093</v>
       </c>
       <c r="Y63" s="16">
-        <v>1.8682615280752231</v>
+        <v>1.939599283522611</v>
       </c>
       <c r="Z63" s="16">
-        <v>12.631374103375165</v>
+        <v>16.456290304921566</v>
       </c>
       <c r="AA63" s="16"/>
       <c r="AB63" s="9"/>
@@ -5131,10 +5131,10 @@
         <v>11.97225303644683</v>
       </c>
       <c r="Y66" s="16">
-        <v>12.374866202127293</v>
+        <v>12.374866202127237</v>
       </c>
       <c r="Z66" s="16">
-        <v>9.3262027687880789</v>
+        <v>9.1015722641562604</v>
       </c>
       <c r="AA66" s="16"/>
       <c r="AB66" s="9"/>
@@ -5276,10 +5276,10 @@
         <v>6.343191279030151</v>
       </c>
       <c r="Y67" s="16">
-        <v>11.812362062585208</v>
+        <v>11.812861283567869</v>
       </c>
       <c r="Z67" s="16">
-        <v>4.1877511000926688</v>
+        <v>3.9267878764013062</v>
       </c>
       <c r="AA67" s="16"/>
       <c r="AB67" s="9"/>
@@ -5421,10 +5421,10 @@
         <v>-5.7016167767752819</v>
       </c>
       <c r="Y68" s="16">
-        <v>5.5982073642570072</v>
+        <v>5.6734224535470332</v>
       </c>
       <c r="Z68" s="16">
-        <v>-0.24455883126562128</v>
+        <v>-9.9564293285126837E-2</v>
       </c>
       <c r="AA68" s="16"/>
       <c r="AB68" s="9"/>
@@ -5566,10 +5566,10 @@
         <v>15.596322074781966</v>
       </c>
       <c r="Y69" s="16">
-        <v>27.245100151352929</v>
+        <v>19.511863741855635</v>
       </c>
       <c r="Z69" s="16">
-        <v>16.944695653043055</v>
+        <v>11.174470270735554</v>
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="9"/>
@@ -5804,10 +5804,10 @@
         <v>18.027381424769544</v>
       </c>
       <c r="Y71" s="16">
-        <v>9.8062116492616127</v>
+        <v>9.475775907390485</v>
       </c>
       <c r="Z71" s="16">
-        <v>3.1511390578989875</v>
+        <v>2.65952420457036</v>
       </c>
       <c r="AA71" s="16"/>
       <c r="AB71" s="9"/>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="78" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:91" x14ac:dyDescent="0.2">
@@ -6117,7 +6117,7 @@
     </row>
     <row r="81" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:91" x14ac:dyDescent="0.2">
@@ -6231,7 +6231,7 @@
         <v>51</v>
       </c>
       <c r="Z85" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA85" s="15"/>
     </row>
@@ -6312,10 +6312,10 @@
         <v>25.085465980438855</v>
       </c>
       <c r="Y87" s="16">
-        <v>2.2964116971613748</v>
+        <v>-0.7982828891638718</v>
       </c>
       <c r="Z87" s="16">
-        <v>6.2123020266576532</v>
+        <v>2.9066293435389809</v>
       </c>
       <c r="AA87" s="16"/>
       <c r="AB87" s="9"/>
@@ -6457,10 +6457,10 @@
         <v>-7.0764173072971772</v>
       </c>
       <c r="Y88" s="16">
-        <v>-0.57276315358845409</v>
+        <v>-0.50265497924146985</v>
       </c>
       <c r="Z88" s="16">
-        <v>10.547945491015767</v>
+        <v>14.335822846036365</v>
       </c>
       <c r="AA88" s="16"/>
       <c r="AB88" s="9"/>
@@ -6895,7 +6895,7 @@
         <v>11.790488710750836</v>
       </c>
       <c r="Z91" s="16">
-        <v>7.7489147496064845</v>
+        <v>7.5267369791114191</v>
       </c>
       <c r="AA91" s="16"/>
       <c r="AB91" s="9"/>
@@ -7037,10 +7037,10 @@
         <v>3.0268439501897717</v>
       </c>
       <c r="Y92" s="16">
-        <v>9.2712874495937996</v>
+        <v>9.2717699600727315</v>
       </c>
       <c r="Z92" s="16">
-        <v>2.2762019577913719</v>
+        <v>2.0214923944202638</v>
       </c>
       <c r="AA92" s="16"/>
       <c r="AB92" s="9"/>
@@ -7182,10 +7182,10 @@
         <v>-9.3442639772588763</v>
       </c>
       <c r="Y93" s="16">
-        <v>3.1493464410568208</v>
+        <v>3.2221268107170289</v>
       </c>
       <c r="Z93" s="16">
-        <v>-2.0838453607496774</v>
+        <v>-1.9438817237103194</v>
       </c>
       <c r="AA93" s="16"/>
       <c r="AB93" s="9"/>
@@ -7327,10 +7327,10 @@
         <v>10.52765958670912</v>
       </c>
       <c r="Y94" s="16">
-        <v>24.328507594561529</v>
+        <v>16.796882434684406</v>
       </c>
       <c r="Z94" s="16">
-        <v>14.88235565017942</v>
+        <v>9.2528206181662114</v>
       </c>
       <c r="AA94" s="16"/>
       <c r="AB94" s="9"/>
@@ -7565,10 +7565,10 @@
         <v>13.880766019080482</v>
       </c>
       <c r="Y96" s="16">
-        <v>7.9340795453600492</v>
+        <v>7.6345777473885335</v>
       </c>
       <c r="Z96" s="16">
-        <v>1.5707781599389392</v>
+        <v>1.1137045508391736</v>
       </c>
       <c r="AA96" s="16"/>
       <c r="AB96" s="9"/>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="102" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="1:96" x14ac:dyDescent="0.2">
@@ -7874,7 +7874,7 @@
     </row>
     <row r="105" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:96" x14ac:dyDescent="0.2">
@@ -8074,10 +8074,10 @@
         <v>135.81750076794691</v>
       </c>
       <c r="Z111" s="16">
-        <v>136.58147374794103</v>
+        <v>136.62879798991659</v>
       </c>
       <c r="AA111" s="16">
-        <v>138.33478264116249</v>
+        <v>138.34921911318173</v>
       </c>
       <c r="AB111" s="9"/>
       <c r="AC111" s="9"/>
@@ -8226,10 +8226,10 @@
         <v>119.08639507135152</v>
       </c>
       <c r="Z112" s="16">
-        <v>122.01006909508571</v>
+        <v>122.00948066664591</v>
       </c>
       <c r="AA112" s="16">
-        <v>124.30951724692233</v>
+        <v>124.27226346725158</v>
       </c>
       <c r="AB112" s="9"/>
       <c r="AC112" s="9"/>
@@ -8679,13 +8679,13 @@
         <v>102.71380956178649</v>
       </c>
       <c r="Y115" s="16">
-        <v>103.21429736762188</v>
+        <v>103.21429736762194</v>
       </c>
       <c r="Z115" s="16">
         <v>103.75384337789058</v>
       </c>
       <c r="AA115" s="16">
-        <v>105.27264933973521</v>
+        <v>105.27342090903301</v>
       </c>
       <c r="AB115" s="9"/>
       <c r="AC115" s="9"/>
@@ -8834,10 +8834,10 @@
         <v>119.28269001316738</v>
       </c>
       <c r="Z116" s="16">
-        <v>122.05657711961888</v>
+        <v>122.05658311242233</v>
       </c>
       <c r="AA116" s="16">
-        <v>124.33782281352453</v>
+        <v>124.336042576229</v>
       </c>
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
@@ -8986,10 +8986,10 @@
         <v>120.18520787138642</v>
       </c>
       <c r="Z117" s="16">
-        <v>123.03851590733323</v>
+        <v>123.03933891373534</v>
       </c>
       <c r="AA117" s="16">
-        <v>125.34970843475458</v>
+        <v>125.35356062040334</v>
       </c>
       <c r="AB117" s="9"/>
       <c r="AC117" s="9"/>
@@ -9138,10 +9138,10 @@
         <v>117.97119183505187</v>
       </c>
       <c r="Z118" s="16">
-        <v>120.73864965047068</v>
+        <v>120.7134703440351</v>
       </c>
       <c r="AA118" s="16">
-        <v>122.90612041355399</v>
+        <v>122.83670155247937</v>
       </c>
       <c r="AB118" s="9"/>
       <c r="AC118" s="9"/>
@@ -9388,10 +9388,10 @@
         <v>118.36893498976184</v>
       </c>
       <c r="Z120" s="16">
-        <v>120.42206115929423</v>
+        <v>120.39375517176722</v>
       </c>
       <c r="AA120" s="16">
-        <v>122.29573309679016</v>
+        <v>122.23432696920786</v>
       </c>
       <c r="AB120" s="9"/>
       <c r="AC120" s="9"/>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="127" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" spans="1:96" x14ac:dyDescent="0.2">
@@ -9519,7 +9519,7 @@
     </row>
     <row r="130" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:96" x14ac:dyDescent="0.2">
@@ -9719,10 +9719,10 @@
         <v>7.5957003813453303</v>
       </c>
       <c r="Z136" s="17">
-        <v>7.116023551720108</v>
+        <v>6.9239750765808461</v>
       </c>
       <c r="AA136" s="17">
-        <v>7.4212620645563581</v>
+        <v>7.0280374453699475</v>
       </c>
       <c r="AB136" s="9"/>
       <c r="AC136" s="9"/>
@@ -9871,10 +9871,10 @@
         <v>8.8908518930043492E-2</v>
       </c>
       <c r="Z137" s="17">
-        <v>8.2481274259500442E-2</v>
+        <v>8.278816676565133E-2</v>
       </c>
       <c r="AA137" s="17">
-        <v>9.0061819408803562E-2</v>
+        <v>9.3914352880311996E-2</v>
       </c>
       <c r="AB137" s="9"/>
       <c r="AC137" s="9"/>
@@ -10023,10 +10023,10 @@
         <v>17.138198310717673</v>
       </c>
       <c r="Z138" s="17">
-        <v>16.508796742162744</v>
+        <v>16.558625998486175</v>
       </c>
       <c r="AA138" s="17">
-        <v>14.830222892683137</v>
+        <v>14.946218808041712</v>
       </c>
       <c r="AB138" s="9"/>
       <c r="AC138" s="9"/>
@@ -10175,10 +10175,10 @@
         <v>0.64794819938506354</v>
       </c>
       <c r="Z139" s="17">
-        <v>0.63637126591366022</v>
+        <v>0.63829205441335091</v>
       </c>
       <c r="AA139" s="17">
-        <v>0.67190731833788009</v>
+        <v>0.67716270155030511</v>
       </c>
       <c r="AB139" s="9"/>
       <c r="AC139" s="9"/>
@@ -10324,13 +10324,13 @@
         <v>15.322103604463949</v>
       </c>
       <c r="Y140" s="17">
-        <v>14.536037664643469</v>
+        <v>14.536037664643475</v>
       </c>
       <c r="Z140" s="17">
-        <v>14.876073613130403</v>
+        <v>14.920974746552304</v>
       </c>
       <c r="AA140" s="17">
-        <v>15.76661833389587</v>
+        <v>15.8572895907709</v>
       </c>
       <c r="AB140" s="9"/>
       <c r="AC140" s="9"/>
@@ -10479,10 +10479,10 @@
         <v>49.866046318649211</v>
       </c>
       <c r="Z141" s="17">
-        <v>50.777094864359093</v>
+        <v>50.930585086729607</v>
       </c>
       <c r="AA141" s="17">
-        <v>51.287376655570924</v>
+        <v>51.559289347397062</v>
       </c>
       <c r="AB141" s="9"/>
       <c r="AC141" s="9"/>
@@ -10631,10 +10631,10 @@
         <v>8.7875247208231126</v>
       </c>
       <c r="Z142" s="17">
-        <v>8.4507683468037555</v>
+        <v>8.4823131368356002</v>
       </c>
       <c r="AA142" s="17">
-        <v>8.1725721339538602</v>
+        <v>8.2543415697317499</v>
       </c>
       <c r="AB142" s="9"/>
       <c r="AC142" s="9"/>
@@ -10783,10 +10783,10 @@
         <v>1.3396358855060975</v>
       </c>
       <c r="Z143" s="17">
-        <v>1.5523903416507314</v>
+        <v>1.4624457336364642</v>
       </c>
       <c r="AA143" s="17">
-        <v>1.7599787815931669</v>
+        <v>1.5837461842580096</v>
       </c>
       <c r="AB143" s="9"/>
       <c r="AC143" s="9"/>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="152" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154" spans="1:96" x14ac:dyDescent="0.2">
@@ -11360,7 +11360,7 @@
     </row>
     <row r="155" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="156" spans="1:96" x14ac:dyDescent="0.2">
@@ -11560,10 +11560,10 @@
         <v>6.6198756386876614</v>
       </c>
       <c r="Z161" s="17">
-        <v>6.2741029207054888</v>
+        <v>6.1012273579894476</v>
       </c>
       <c r="AA161" s="17">
-        <v>6.5608133208448685</v>
+        <v>6.209412908549881</v>
       </c>
       <c r="AB161" s="9"/>
       <c r="AC161" s="9"/>
@@ -11712,10 +11712,10 @@
         <v>8.8372871569088893E-2</v>
       </c>
       <c r="Z162" s="17">
-        <v>8.1407748778777989E-2</v>
+        <v>8.1691834325035531E-2</v>
       </c>
       <c r="AA162" s="17">
-        <v>8.8602839690482743E-2</v>
+        <v>9.2374254695205854E-2</v>
       </c>
       <c r="AB162" s="9"/>
       <c r="AC162" s="9"/>
@@ -11864,10 +11864,10 @@
         <v>16.487304894162005</v>
       </c>
       <c r="Z163" s="17">
-        <v>15.82593703972875</v>
+        <v>15.869973971885504</v>
       </c>
       <c r="AA163" s="17">
-        <v>14.197958091568955</v>
+        <v>14.301823969462763</v>
       </c>
       <c r="AB163" s="9"/>
       <c r="AC163" s="9"/>
@@ -12016,10 +12016,10 @@
         <v>0.65119793180576946</v>
       </c>
       <c r="Z164" s="17">
-        <v>0.63611896801599732</v>
+        <v>0.63788901978404255</v>
       </c>
       <c r="AA164" s="17">
-        <v>0.66672706563412054</v>
+        <v>0.67160454108101408</v>
       </c>
       <c r="AB164" s="9"/>
       <c r="AC164" s="9"/>
@@ -12168,10 +12168,10 @@
         <v>16.67031933770317</v>
       </c>
       <c r="Z165" s="17">
-        <v>17.265938187233381</v>
+        <v>17.313982037443655</v>
       </c>
       <c r="AA165" s="17">
-        <v>18.316154857834391</v>
+        <v>18.412103491522334</v>
       </c>
       <c r="AB165" s="9"/>
       <c r="AC165" s="9"/>
@@ -12320,10 +12320,10 @@
         <v>49.484051661117512</v>
       </c>
       <c r="Z166" s="17">
-        <v>50.09711535048681</v>
+        <v>50.23673639986179</v>
       </c>
       <c r="AA166" s="17">
-        <v>50.445047088455233</v>
+        <v>50.687756356133427</v>
       </c>
       <c r="AB166" s="9"/>
       <c r="AC166" s="9"/>
@@ -12472,10 +12472,10 @@
         <v>8.6547251597979624</v>
       </c>
       <c r="Z167" s="17">
-        <v>8.2710599619738741</v>
+        <v>8.299926999790209</v>
       </c>
       <c r="AA167" s="17">
-        <v>7.9734585176838886</v>
+        <v>8.0489447715447646</v>
       </c>
       <c r="AB167" s="9"/>
       <c r="AC167" s="9"/>
@@ -12624,10 +12624,10 @@
         <v>1.3441525051568415</v>
       </c>
       <c r="Z168" s="17">
-        <v>1.5483198230769124</v>
+        <v>1.4585723789202967</v>
       </c>
       <c r="AA168" s="17">
-        <v>1.7512382182880746</v>
+        <v>1.5759797070106318</v>
       </c>
       <c r="AB168" s="9"/>
       <c r="AC168" s="9"/>
